--- a/web/public/forms/jajae-balju.xlsx
+++ b/web/public/forms/jajae-balju.xlsx
@@ -617,7 +617,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="25" t="inlineStr">

--- a/web/public/forms/jajae-balju.xlsx
+++ b/web/public/forms/jajae-balju.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자재발주서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'자재발주서'!$A$1:$X$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -140,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -211,19 +209,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -966,10 +956,7 @@
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9">
-        <f>IF(C17="","",COUNTA(C17:C17))</f>
-        <v/>
-      </c>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="5" t="n"/>
@@ -987,10 +974,7 @@
       <c r="P17" s="12" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="13">
-        <f>IF(OR(N17="",P17=""),"",INT(ROUND(N17*P17,6)))</f>
-        <v/>
-      </c>
+      <c r="S17" s="13" t="n"/>
       <c r="T17" s="5" t="n"/>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="10" t="n"/>
@@ -998,10 +982,7 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9">
-        <f>IF(C18="","",COUNTA(C17:C18))</f>
-        <v/>
-      </c>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="5" t="n"/>
@@ -1019,10 +1000,7 @@
       <c r="P18" s="12" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="13">
-        <f>IF(OR(N18="",P18=""),"",INT(ROUND(N18*P18,6)))</f>
-        <v/>
-      </c>
+      <c r="S18" s="13" t="n"/>
       <c r="T18" s="5" t="n"/>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="10" t="n"/>
@@ -1030,10 +1008,7 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9">
-        <f>IF(C19="","",COUNTA(C17:C19))</f>
-        <v/>
-      </c>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="5" t="n"/>
@@ -1051,10 +1026,7 @@
       <c r="P19" s="12" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="5" t="n"/>
-      <c r="S19" s="13">
-        <f>IF(OR(N19="",P19=""),"",INT(ROUND(N19*P19,6)))</f>
-        <v/>
-      </c>
+      <c r="S19" s="13" t="n"/>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="10" t="n"/>
@@ -1062,10 +1034,7 @@
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9">
-        <f>IF(C20="","",COUNTA(C17:C20))</f>
-        <v/>
-      </c>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="5" t="n"/>
@@ -1083,10 +1052,7 @@
       <c r="P20" s="12" t="n"/>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="5" t="n"/>
-      <c r="S20" s="13">
-        <f>IF(OR(N20="",P20=""),"",INT(ROUND(N20*P20,6)))</f>
-        <v/>
-      </c>
+      <c r="S20" s="13" t="n"/>
       <c r="T20" s="5" t="n"/>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="10" t="n"/>
@@ -1094,10 +1060,7 @@
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9">
-        <f>IF(C21="","",COUNTA(C17:C21))</f>
-        <v/>
-      </c>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="5" t="n"/>
@@ -1115,10 +1078,7 @@
       <c r="P21" s="12" t="n"/>
       <c r="Q21" s="5" t="n"/>
       <c r="R21" s="5" t="n"/>
-      <c r="S21" s="13">
-        <f>IF(OR(N21="",P21=""),"",INT(ROUND(N21*P21,6)))</f>
-        <v/>
-      </c>
+      <c r="S21" s="13" t="n"/>
       <c r="T21" s="5" t="n"/>
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="10" t="n"/>
@@ -1126,10 +1086,7 @@
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9">
-        <f>IF(C22="","",COUNTA(C17:C22))</f>
-        <v/>
-      </c>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="5" t="n"/>
@@ -1147,10 +1104,7 @@
       <c r="P22" s="12" t="n"/>
       <c r="Q22" s="5" t="n"/>
       <c r="R22" s="5" t="n"/>
-      <c r="S22" s="13">
-        <f>IF(OR(N22="",P22=""),"",INT(ROUND(N22*P22,6)))</f>
-        <v/>
-      </c>
+      <c r="S22" s="13" t="n"/>
       <c r="T22" s="5" t="n"/>
       <c r="U22" s="5" t="n"/>
       <c r="V22" s="10" t="n"/>
@@ -1158,10 +1112,7 @@
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9">
-        <f>IF(C23="","",COUNTA(C17:C23))</f>
-        <v/>
-      </c>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="5" t="n"/>
@@ -1179,10 +1130,7 @@
       <c r="P23" s="12" t="n"/>
       <c r="Q23" s="5" t="n"/>
       <c r="R23" s="5" t="n"/>
-      <c r="S23" s="13">
-        <f>IF(OR(N23="",P23=""),"",INT(ROUND(N23*P23,6)))</f>
-        <v/>
-      </c>
+      <c r="S23" s="13" t="n"/>
       <c r="T23" s="5" t="n"/>
       <c r="U23" s="5" t="n"/>
       <c r="V23" s="10" t="n"/>
@@ -1190,10 +1138,7 @@
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9">
-        <f>IF(C24="","",COUNTA(C17:C24))</f>
-        <v/>
-      </c>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="5" t="n"/>
@@ -1211,10 +1156,7 @@
       <c r="P24" s="12" t="n"/>
       <c r="Q24" s="5" t="n"/>
       <c r="R24" s="5" t="n"/>
-      <c r="S24" s="13">
-        <f>IF(OR(N24="",P24=""),"",INT(ROUND(N24*P24,6)))</f>
-        <v/>
-      </c>
+      <c r="S24" s="13" t="n"/>
       <c r="T24" s="5" t="n"/>
       <c r="U24" s="5" t="n"/>
       <c r="V24" s="10" t="n"/>
@@ -1222,10 +1164,7 @@
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9">
-        <f>IF(C25="","",COUNTA(C17:C25))</f>
-        <v/>
-      </c>
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="5" t="n"/>
@@ -1243,10 +1182,7 @@
       <c r="P25" s="12" t="n"/>
       <c r="Q25" s="5" t="n"/>
       <c r="R25" s="5" t="n"/>
-      <c r="S25" s="13">
-        <f>IF(OR(N25="",P25=""),"",INT(ROUND(N25*P25,6)))</f>
-        <v/>
-      </c>
+      <c r="S25" s="13" t="n"/>
       <c r="T25" s="5" t="n"/>
       <c r="U25" s="5" t="n"/>
       <c r="V25" s="10" t="n"/>
@@ -1254,10 +1190,7 @@
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9">
-        <f>IF(C26="","",COUNTA(C17:C26))</f>
-        <v/>
-      </c>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="5" t="n"/>
@@ -1275,10 +1208,7 @@
       <c r="P26" s="12" t="n"/>
       <c r="Q26" s="5" t="n"/>
       <c r="R26" s="5" t="n"/>
-      <c r="S26" s="13">
-        <f>IF(OR(N26="",P26=""),"",INT(ROUND(N26*P26,6)))</f>
-        <v/>
-      </c>
+      <c r="S26" s="13" t="n"/>
       <c r="T26" s="5" t="n"/>
       <c r="U26" s="5" t="n"/>
       <c r="V26" s="10" t="n"/>
@@ -1286,10 +1216,7 @@
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9">
-        <f>IF(C27="","",COUNTA(C17:C27))</f>
-        <v/>
-      </c>
+      <c r="A27" s="9" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="5" t="n"/>
@@ -1307,10 +1234,7 @@
       <c r="P27" s="12" t="n"/>
       <c r="Q27" s="5" t="n"/>
       <c r="R27" s="5" t="n"/>
-      <c r="S27" s="13">
-        <f>IF(OR(N27="",P27=""),"",INT(ROUND(N27*P27,6)))</f>
-        <v/>
-      </c>
+      <c r="S27" s="13" t="n"/>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5" t="n"/>
       <c r="V27" s="10" t="n"/>
@@ -1318,10 +1242,7 @@
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9">
-        <f>IF(C28="","",COUNTA(C17:C28))</f>
-        <v/>
-      </c>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="5" t="n"/>
@@ -1339,10 +1260,7 @@
       <c r="P28" s="12" t="n"/>
       <c r="Q28" s="5" t="n"/>
       <c r="R28" s="5" t="n"/>
-      <c r="S28" s="13">
-        <f>IF(OR(N28="",P28=""),"",INT(ROUND(N28*P28,6)))</f>
-        <v/>
-      </c>
+      <c r="S28" s="13" t="n"/>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="n"/>
       <c r="V28" s="10" t="n"/>
@@ -1372,10 +1290,7 @@
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n"/>
       <c r="R29" s="5" t="n"/>
-      <c r="S29" s="15">
-        <f>SUM(S17:S28)</f>
-        <v/>
-      </c>
+      <c r="S29" s="15" t="n"/>
       <c r="T29" s="5" t="n"/>
       <c r="U29" s="5" t="n"/>
       <c r="V29" s="14" t="inlineStr"/>
@@ -1394,10 +1309,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="13">
-        <f>IF(COUNT(S17:S28)=0,"",SUM(S17:S28))</f>
-        <v/>
-      </c>
+      <c r="G31" s="13" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
@@ -1433,10 +1345,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
-      <c r="K32" s="13">
-        <f>IF(G31="","",INT(ROUND(G31*G32,6)))</f>
-        <v/>
-      </c>
+      <c r="K32" s="13" t="n"/>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="5" t="n"/>
       <c r="N32" s="5" t="n"/>
@@ -1462,10 +1371,7 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="13">
-        <f>IF(G31="","",G31+K32)</f>
-        <v/>
-      </c>
+      <c r="G33" s="13" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
@@ -1495,10 +1401,7 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
-      <c r="G34" s="17">
-        <f>G33</f>
-        <v/>
-      </c>
+      <c r="G34" s="17" t="n"/>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
@@ -1563,6 +1466,7 @@
       </c>
     </row>
     <row r="42" ht="6" customHeight="1"/>
+    <row r="43"/>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
@@ -1737,1279 +1641,6 @@
     <mergeCell ref="A36:X36"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <conditionalFormatting sqref="N17:N28">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(N17),MOD(N17,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>자 재 발 주 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발주번호</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>PO-2026-031</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발주일자</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="n">
-        <v>46114</v>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  납품 장소</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 현장 자재 야적장 (가나시 다라동 123-4)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  납품 기한</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="7" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  결제 조건</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>납품 월말 마감 · 다음 달 25일 현금</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="6" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공급자 상호</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>예시관산업(주)</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  사업자등록번호</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  담당자·연락처</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>영업팀 김○○ · 010-0000-0000</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>품  명</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>규  격</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="8" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>단  가</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="8" t="inlineStr">
-        <is>
-          <t>금  액</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9">
-        <f>IF(C17="","",COUNTA(C17:C17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>PE 이중벽관</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>D600, L=6m</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="11" t="n">
-        <v>822</v>
-      </c>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="12" t="n">
-        <v>86140</v>
-      </c>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="13">
-        <f>IF(OR(N17="",P17=""),"",INT(ROUND(N17*P17,6)))</f>
-        <v/>
-      </c>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="10" t="inlineStr">
-        <is>
-          <t>KS M 3600</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9">
-        <f>IF(C18="","",COUNTA(C17:C18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>고무링</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>D600</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="11" t="n">
-        <v>138</v>
-      </c>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="12" t="n">
-        <v>4300</v>
-      </c>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="13">
-        <f>IF(OR(N18="",P18=""),"",INT(ROUND(N18*P18,6)))</f>
-        <v/>
-      </c>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="10" t="inlineStr"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9">
-        <f>IF(C19="","",COUNTA(C17:C19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>집수정(PC)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>1.2×1.2×1.5</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="12" t="n">
-        <v>412000</v>
-      </c>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="13">
-        <f>IF(OR(N19="",P19=""),"",INT(ROUND(N19*P19,6)))</f>
-        <v/>
-      </c>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="10" t="inlineStr">
-        <is>
-          <t>뚜껑 포함</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="9">
-        <f>IF(C20="","",COUNTA(C17:C20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>운반·하차</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>25톤 트럭</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>식</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="12" t="n">
-        <v>1850000</v>
-      </c>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="13">
-        <f>IF(OR(N20="",P20=""),"",INT(ROUND(N20*P20,6)))</f>
-        <v/>
-      </c>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="10" t="inlineStr">
-        <is>
-          <t>현장 하차 포함</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9">
-        <f>IF(C21="","",COUNTA(C17:C21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="12" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="13">
-        <f>IF(OR(N21="",P21=""),"",INT(ROUND(N21*P21,6)))</f>
-        <v/>
-      </c>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="10" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9">
-        <f>IF(C22="","",COUNTA(C17:C22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="10" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="13">
-        <f>IF(OR(N22="",P22=""),"",INT(ROUND(N22*P22,6)))</f>
-        <v/>
-      </c>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="10" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9">
-        <f>IF(C23="","",COUNTA(C17:C23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="12" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="13">
-        <f>IF(OR(N23="",P23=""),"",INT(ROUND(N23*P23,6)))</f>
-        <v/>
-      </c>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="10" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9">
-        <f>IF(C24="","",COUNTA(C17:C24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="10" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="12" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="13">
-        <f>IF(OR(N24="",P24=""),"",INT(ROUND(N24*P24,6)))</f>
-        <v/>
-      </c>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="10" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9">
-        <f>IF(C25="","",COUNTA(C17:C25))</f>
-        <v/>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="10" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="12" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="13">
-        <f>IF(OR(N25="",P25=""),"",INT(ROUND(N25*P25,6)))</f>
-        <v/>
-      </c>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="10" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9">
-        <f>IF(C26="","",COUNTA(C17:C26))</f>
-        <v/>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="10" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="11" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="12" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="13">
-        <f>IF(OR(N26="",P26=""),"",INT(ROUND(N26*P26,6)))</f>
-        <v/>
-      </c>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="10" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9">
-        <f>IF(C27="","",COUNTA(C17:C27))</f>
-        <v/>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="12" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="13">
-        <f>IF(OR(N27="",P27=""),"",INT(ROUND(N27*P27,6)))</f>
-        <v/>
-      </c>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="10" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9">
-        <f>IF(C28="","",COUNTA(C17:C28))</f>
-        <v/>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="10" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="12" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="13">
-        <f>IF(OR(N28="",P28=""),"",INT(ROUND(N28*P28,6)))</f>
-        <v/>
-      </c>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="5" t="n"/>
-      <c r="V28" s="10" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>합        계</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="15">
-        <f>SUM(S17:S28)</f>
-        <v/>
-      </c>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="5" t="n"/>
-      <c r="V29" s="14" t="inlineStr"/>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공급가액</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="13">
-        <f>IF(COUNT(S17:S28)=0,"",SUM(S17:S28))</f>
-        <v/>
-      </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="5" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="5" t="n"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  부가가치세</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="13">
-        <f>IF(G31="","",INT(ROUND(G31*G32,6)))</f>
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="5" t="n"/>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="5" t="n"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발주 총액</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="13">
-        <f>IF(G31="","",G31+K32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="5" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발주 총액(한글)</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="17">
-        <f>G33</f>
-        <v/>
-      </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>위와 같이 발주하오니 납품 기한까지 납품하여 주시기 바랍니다. 규격·수량이 다르면 납품 전에 알려 주시기 바랍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="10" customHeight="1"/>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="19" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="20" t="inlineStr"/>
-      <c r="K40" s="21" t="inlineStr">
-        <is>
-          <t>발주 담당</t>
-        </is>
-      </c>
-      <c r="Q40" s="22" t="inlineStr">
-        <is>
-          <t>한자재</t>
-        </is>
-      </c>
-      <c r="U40" s="23" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="20" t="inlineStr"/>
-      <c r="K41" s="21" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q41" s="22" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U41" s="23" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="148">
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="V24:X24"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="S23:U23"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="G34:X34"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="S24:U24"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="P28:R28"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="U40:X40"/>
-    <mergeCell ref="K32:X32"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="V21:X21"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="S25:U25"/>
-    <mergeCell ref="G31:X31"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G12:X12"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="S27:U27"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="V23:X23"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="S28:U28"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="V27:X27"/>
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="G33:X33"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="V25:X25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="H25:K25"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="S26:U26"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="A44:X44"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="Q40:T40"/>
-    <mergeCell ref="P22:R22"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="K41:P41"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="G13:X13"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="V26:X26"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="S29:U29"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="S22:U22"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="A39:X39"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="V28:X28"/>
-    <mergeCell ref="K40:P40"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="Q41:T41"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="G14:X14"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="A29:R29"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <conditionalFormatting sqref="N17:N28">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(N17),MOD(N17,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/web/public/forms/jajae-balju.xlsx
+++ b/web/public/forms/jajae-balju.xlsx
@@ -607,7 +607,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
